--- a/counselor_forms/002_marriage_survey--counselor_forms.xlsx
+++ b/counselor_forms/002_marriage_survey--counselor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -538,23 +538,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>marital_status</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>What is your current marital status?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Describe your relationship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Is this form assigned to you?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>What is your ID number?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>relationship_category</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>How do you categorize your marriage?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Please describe yourself</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,40 +699,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>marital_category</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Marital Category</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,21 +745,67 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>self_description</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Self Description</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>are_in_relationship</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Are you in a relationship?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>other_description</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Other Description</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -776,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -804,170 +850,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>marital_status_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>marital_status_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>marital_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>divorced</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Divorced</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>marital_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>widowed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Widowed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>relationship_category_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>traditional</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Traditional</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>relationship_category_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>modern</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Modern</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>relationship_category_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>relationship_category_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>marital_category_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>traditional</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Traditional</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>marital_category_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>modern</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Modern</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>marital_category_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>marital_category_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>assigned_tool_2_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>assigned_tool_2_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>are_in_relationship_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>are_in_relationship_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
